--- a/stories/arbres/TREE-COL-012.xlsx
+++ b/stories/arbres/TREE-COL-012.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1163,7 +1180,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules tient la main de papa au marché. Ça sent le pain chaud. Papa dit : on salue. On dit bonjour. On dit s'il te plaît. On dit merci. Jules répète les trois mots. Bonjour. S'il te plaît. Merci.</t>
+          <t>Jules tient la main de papa au marché. Ça sent le pain chaud. On salue. On dit bonjour. On dit s'il te plaît. On dit merci. Jules répète les trois mots. Bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1301,6 +1318,13 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Jules tient la main de papa au marché. Ça sent le pain chaud.
+papa|On salue. On dit bonjour. On dit s'il te plaît. On dit merci.
+narrateur|Jules répète les trois mots. Bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1487,6 +1511,11 @@
         <v>8</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangerie, l'étal des fruits, ou la fromagerie.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1649,6 +1678,11 @@
         <v>8</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|À la boulangerie, Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Le pain est chaud.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1825,6 +1859,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|À la boulangerie, quels mots ?</t>
         </is>
       </c>
     </row>
@@ -1993,6 +2032,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a dit bonjour, s'il te plaît, merci.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2179,6 +2223,11 @@
         <v>8</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2341,6 +2390,11 @@
         <v>8</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Jules dit bonjour à la boulangère. S'il te plaît. Merci. Le pain sent bon.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2527,6 +2581,11 @@
         <v>8</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2689,6 +2748,11 @@
         <v>8</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2851,6 +2915,11 @@
         <v>8</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3013,6 +3082,11 @@
         <v>8</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3175,6 +3249,11 @@
         <v>8</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3337,6 +3416,11 @@
         <v>8</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3499,6 +3583,11 @@
         <v>8</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3661,6 +3750,11 @@
         <v>8</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Le voisin sourit. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3847,6 +3941,11 @@
         <v>8</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4009,6 +4108,11 @@
         <v>8</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4171,6 +4275,11 @@
         <v>8</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4333,6 +4442,11 @@
         <v>8</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4495,6 +4609,11 @@
         <v>8</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4657,6 +4776,11 @@
         <v>8</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4819,6 +4943,11 @@
         <v>8</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -4981,6 +5110,11 @@
         <v>8</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|La maîtresse est là. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5167,6 +5301,11 @@
         <v>8</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5329,6 +5468,11 @@
         <v>8</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5491,6 +5635,11 @@
         <v>8</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5653,6 +5802,11 @@
         <v>8</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5815,6 +5969,11 @@
         <v>8</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -5977,6 +6136,11 @@
         <v>8</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6139,6 +6303,11 @@
         <v>8</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6301,6 +6470,11 @@
         <v>8</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|À l'étal, Jules dit bonjour. Il dit s'il te plaît pour une pomme. Il dit merci.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6477,6 +6651,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|À l'étal, quels mots ?</t>
         </is>
       </c>
     </row>
@@ -6645,6 +6824,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6833,6 +7017,11 @@
       <c r="AV35" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -6997,6 +7186,11 @@
         <v>8</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|À l'étal, la boulangère passe. Bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7183,6 +7377,11 @@
         <v>8</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7345,6 +7544,11 @@
         <v>8</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7507,6 +7711,11 @@
         <v>8</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7669,6 +7878,11 @@
         <v>8</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7831,6 +8045,11 @@
         <v>8</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -7993,6 +8212,11 @@
         <v>8</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8155,6 +8379,11 @@
         <v>8</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8317,6 +8546,11 @@
         <v>8</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Le voisin prend une poire. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8503,6 +8737,11 @@
         <v>8</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8665,6 +8904,11 @@
         <v>8</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8827,6 +9071,11 @@
         <v>8</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -8989,6 +9238,11 @@
         <v>8</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9151,6 +9405,11 @@
         <v>8</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9313,6 +9572,11 @@
         <v>8</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9475,6 +9739,11 @@
         <v>8</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9637,6 +9906,11 @@
         <v>8</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|La maîtresse choisit des fraises. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9823,6 +10097,11 @@
         <v>8</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -9985,6 +10264,11 @@
         <v>8</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10147,6 +10431,11 @@
         <v>8</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10309,6 +10598,11 @@
         <v>8</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10471,6 +10765,11 @@
         <v>8</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10633,6 +10932,11 @@
         <v>8</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10795,6 +11099,11 @@
         <v>8</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10957,6 +11266,11 @@
         <v>8</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|À la fromagerie, Jules dit bonjour. S'il te plaît. Merci. Papa sourit.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11133,6 +11447,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|À la fromagerie, quels mots ?</t>
         </is>
       </c>
     </row>
@@ -11297,6 +11616,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Jules a salué. Les trois mots sont là.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11485,6 +11809,11 @@
       <c r="AV63" s="2" t="inlineStr">
         <is>
           <t>prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
     </row>
@@ -11649,6 +11978,11 @@
         <v>8</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|À la fromagerie, la boulangère salue. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11835,6 +12169,11 @@
         <v>8</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -11997,6 +12336,11 @@
         <v>8</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12159,6 +12503,11 @@
         <v>8</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12321,6 +12670,11 @@
         <v>8</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12483,6 +12837,11 @@
         <v>8</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12645,6 +13004,11 @@
         <v>8</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12807,6 +13171,11 @@
         <v>8</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -12969,6 +13338,11 @@
         <v>8</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Le voisin goûte. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13155,6 +13529,11 @@
         <v>8</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13317,6 +13696,11 @@
         <v>8</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13479,6 +13863,11 @@
         <v>8</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13641,6 +14030,11 @@
         <v>8</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13803,6 +14197,11 @@
         <v>8</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -13965,6 +14364,11 @@
         <v>8</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14127,6 +14531,11 @@
         <v>8</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14289,6 +14698,11 @@
         <v>8</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|La maîtresse attend. Jules dit bonjour. S'il te plaît. Merci.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14475,6 +14889,11 @@
         <v>8</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14637,6 +15056,11 @@
         <v>8</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14799,6 +15223,11 @@
         <v>8</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -14961,6 +15390,11 @@
         <v>8</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15123,6 +15557,11 @@
         <v>8</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15285,6 +15724,11 @@
         <v>8</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15447,6 +15891,11 @@
         <v>8</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15465,7 +15914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15489,6 +15938,13 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>ch2C: prompt réécrit pour coller aux options</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-COL-012.xlsx
+++ b/stories/arbres/TREE-COL-012.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1325,6 +1330,7 @@
 narrateur|Jules répète les trois mots. Bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1516,6 +1522,7 @@
           <t>narrateur|On peut prendre la boulangerie, l'étal des fruits, ou la fromagerie.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1683,6 +1690,7 @@
           <t>narrateur|À la boulangerie, Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Le pain est chaud.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1866,6 +1874,7 @@
           <t>narrateur|À la boulangerie, quels mots ?</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2037,6 +2046,7 @@
           <t>narrateur|Jules a dit bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2228,6 +2238,7 @@
           <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2395,6 +2406,7 @@
           <t>narrateur|Jules dit bonjour à la boulangère. S'il te plaît. Merci. Le pain sent bon.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2586,6 +2598,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2753,6 +2766,7 @@
           <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2920,6 +2934,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3087,6 +3102,7 @@
           <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3254,6 +3270,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3421,6 +3438,7 @@
           <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3588,6 +3606,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3755,6 +3774,7 @@
           <t>narrateur|Le voisin sourit. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3946,6 +3966,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4113,6 +4134,7 @@
           <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4280,6 +4302,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4447,6 +4470,7 @@
           <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4614,6 +4638,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4781,6 +4806,7 @@
           <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4948,6 +4974,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5115,6 +5142,7 @@
           <t>narrateur|La maîtresse est là. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5306,6 +5334,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5473,6 +5502,7 @@
           <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5640,6 +5670,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5807,6 +5838,7 @@
           <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5974,6 +6006,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6141,6 +6174,7 @@
           <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6308,6 +6342,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6475,6 +6510,7 @@
           <t>narrateur|À l'étal, Jules dit bonjour. Il dit s'il te plaît pour une pomme. Il dit merci.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6658,6 +6694,7 @@
           <t>narrateur|À l'étal, quels mots ?</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6829,6 +6866,7 @@
           <t>narrateur|Oui. Bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7024,6 +7062,7 @@
           <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7191,6 +7230,7 @@
           <t>narrateur|À l'étal, la boulangère passe. Bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7382,6 +7422,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7549,6 +7590,7 @@
           <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7716,6 +7758,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7883,6 +7926,7 @@
           <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8050,6 +8094,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8217,6 +8262,7 @@
           <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8384,6 +8430,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8551,6 +8598,7 @@
           <t>narrateur|Le voisin prend une poire. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8742,6 +8790,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8909,6 +8958,7 @@
           <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9076,6 +9126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9243,6 +9294,7 @@
           <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9410,6 +9462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9577,6 +9630,7 @@
           <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9744,6 +9798,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9911,6 +9966,7 @@
           <t>narrateur|La maîtresse choisit des fraises. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10102,6 +10158,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10269,6 +10326,7 @@
           <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10436,6 +10494,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10603,6 +10662,7 @@
           <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10770,6 +10830,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10937,6 +10998,7 @@
           <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11104,6 +11166,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11271,6 +11334,7 @@
           <t>narrateur|À la fromagerie, Jules dit bonjour. S'il te plaît. Merci. Papa sourit.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11454,6 +11518,7 @@
           <t>narrateur|À la fromagerie, quels mots ?</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11621,6 +11686,7 @@
           <t>narrateur|Jules a salué. Les trois mots sont là.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11816,6 +11882,7 @@
           <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11983,6 +12050,7 @@
           <t>narrateur|À la fromagerie, la boulangère salue. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12174,6 +12242,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12341,6 +12410,7 @@
           <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12508,6 +12578,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12675,6 +12746,7 @@
           <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12842,6 +12914,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13009,6 +13082,7 @@
           <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13176,6 +13250,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13343,6 +13418,7 @@
           <t>narrateur|Le voisin goûte. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13534,6 +13610,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13701,6 +13778,7 @@
           <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13868,6 +13946,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14035,6 +14114,7 @@
           <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14202,6 +14282,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14369,6 +14450,7 @@
           <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14536,6 +14618,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14703,6 +14786,7 @@
           <t>narrateur|La maîtresse attend. Jules dit bonjour. S'il te plaît. Merci.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14894,6 +14978,7 @@
           <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15061,6 +15146,7 @@
           <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15228,6 +15314,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15395,6 +15482,7 @@
           <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15562,6 +15650,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15729,6 +15818,7 @@
           <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15896,6 +15986,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15914,7 +16005,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15945,6 +16036,20 @@
       <c r="A4" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -15959,7 +16064,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16146,6 +16251,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-COL-012.xlsx
+++ b/stories/arbres/TREE-COL-012.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Jules dit bonjour, s'il te plaît, merci</t>
+          <t>La bâche du marché d'Aniss</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Une bâche claque au-dessus des caisses. Aniss tient le filet. Au marché, il dit bonjour, s'il te plaît, merci.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Jules tient la main de papa au marché. Ça sent le pain chaud. On salue. On dit bonjour. On dit s'il te plaît. On dit merci. Jules répète les trois mots. Bonjour. S'il te plaît. Merci.</t>
+          <t>Une bâche claque au-dessus des caisses. Une fraise brille, encore mouillée. L'eau tremble dans une ornière. Tu entends les pièces, Aniss ? Elles font tic, dans le porte-monnaie. Ça sent l'oignon et le savon. Le filet de maman est encore vide. Il est un peu rêche, contre la jambe. Un pigeon picore près d'une caisse. En ce moment, Aniss tient le filet. Il est au marché, avec papa et maman. On dit bonjour, d'accord ? Bonjour. Si tu veux une fraise ? S'il te plaît. Bravo. Et ensuite ? Merci. Bonjour. S'il te plaît. Merci. La boulangerie sent le four, plus loin. L'étal des fruits est tout rouge. La fromagerie est un peu fraîche. Tu restes près de nous. Oui, maman. Le filet va se remplir, tout doux. Tu es prêt ? Oui, papa. Une feuille collée au pavé, tout plat. Le soleil revient sur la bâche. Ça sent aussi le thym, tout bas.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,12 +1337,43 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Jules tient la main de papa au marché. Ça sent le pain chaud.
-papa|On salue. On dit bonjour. On dit s'il te plaît. On dit merci.
-narrateur|Jules répète les trois mots. Bonjour. S'il te plaît. Merci.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Une bâche claque au-dessus des caisses.
+narrateur|Une fraise brille, encore mouillée.
+narrateur|L'eau tremble dans une ornière.
+papa|Tu entends les pièces, Aniss ?
+maman|Elles font tic, dans le porte-monnaie.
+narrateur|Ça sent l'oignon et le savon.
+narrateur|Le filet de maman est encore vide.
+narrateur|Il est un peu rêche, contre la jambe.
+narrateur|Un pigeon picore près d'une caisse.
+narrateur|En ce moment, Aniss tient le filet.
+narrateur|Il est au marché, avec papa et maman.
+maman|On dit bonjour, d'accord ?
+enfant-m|Bonjour.
+papa|Si tu veux une fraise ?
+enfant-m|S'il te plaît.
+maman|Bravo.
+papa|Et ensuite ?
+enfant-m|Merci.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|La boulangerie sent le four, plus loin.
+narrateur|L'étal des fruits est tout rouge.
+narrateur|La fromagerie est un peu fraîche.
+maman|Tu restes près de nous.
+enfant-m|Oui, maman.
+papa|Le filet va se remplir, tout doux.
+maman|Tu es prêt ?
+enfant-m|Oui, papa.
+narrateur|Une feuille collée au pavé, tout plat.
+narrateur|Le soleil revient sur la bâche.
+narrateur|Ça sent aussi le thym, tout bas.</t>
+        </is>
+      </c>
+      <c r="AX2" t="inlineStr">
+        <is>
+          <t>bache,marche</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1355,7 +1398,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangerie, l'étal des fruits, ou la fromagerie.</t>
+          <t>Où va Aniss, d'abord ? La boulangerie, l'étal des fruits, ou la fromagerie.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1519,7 +1562,8 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangerie, l'étal des fruits, ou la fromagerie.</t>
+          <t>narrateur|Où va Aniss, d'abord ?
+maman|La boulangerie, l'étal des fruits, ou la fromagerie.</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr"/>
@@ -1547,7 +1591,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>À la boulangerie, Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Le pain est chaud.</t>
+          <t>Aniss pousse la porte de la boulangerie. Un grelot tinte, tout aigu. L'air sent le beurre, tout chaud. Des croûtes dorées sont alignées. Bonjour. Bonjour. Tu veux un petit pain, Aniss ? S'il te plaît. Le papier du sachet est un peu rêche. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le bois du comptoir est lisse, tout chaud.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1687,10 +1731,27 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|À la boulangerie, Jules dit bonjour. Il dit s'il te plaît. Il dit merci. Le pain est chaud.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss pousse la porte de la boulangerie.
+narrateur|Un grelot tinte, tout aigu.
+narrateur|L'air sent le beurre, tout chaud.
+narrateur|Des croûtes dorées sont alignées.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu veux un petit pain, Aniss ?
+enfant-m|S'il te plaît.
+narrateur|Le papier du sachet est un peu rêche.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+maman|Tu as dit les trois mots.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Le bois du comptoir est lisse, tout chaud.</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>cloche,papier</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1715,7 +1776,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>À la boulangerie, quels mots ?</t>
+          <t>Aniss veut le petit pain. Que dit-il ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1871,7 +1932,8 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|À la boulangerie, quels mots ?</t>
+          <t>narrateur|Aniss veut le petit pain.
+maman|Que dit-il ?</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr"/>
@@ -1899,7 +1961,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Jules a dit bonjour, s'il te plaît, merci.</t>
+          <t>Oui. Bonjour. S'il te plaît. Merci. Aniss tient le sachet, tout calme. Bravo, Aniss. Tu as fait du bon travail. Merci, papa. On continue, tout doux.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2043,7 +2105,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Jules a dit bonjour, s'il te plaît, merci.</t>
+          <t>narrateur|Oui.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Aniss tient le sachet, tout calme.
+papa|Bravo, Aniss.
+papa|Tu as fait du bon travail.
+enfant-m|Merci, papa.
+maman|On continue, tout doux.</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr"/>
@@ -2071,7 +2139,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>Qui est là, près d'Aniss ? La boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2235,7 +2303,8 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>narrateur|Qui est là, près d'Aniss ?
+papa|La boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr"/>
@@ -2263,7 +2332,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Jules dit bonjour à la boulangère. S'il te plaît. Merci. Le pain sent bon.</t>
+          <t>Aniss voit la boulangère, à la boulangerie. De la farine blanche reste sur le tablier. Le tablier sent le four, tout chaud. Bonjour. Bonjour. Tu restes près de nous, Aniss. Oui, maman. Tu veux que je tienne le filet ? S'il te plaît. Le filet est rêche, un peu lourd déjà. Merci, papa. Bravo. Tu as dit les mots gentils. Bonjour. S'il te plaît. Merci. Aniss reste tout près de la jambe de maman.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2403,7 +2472,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Jules dit bonjour à la boulangère. S'il te plaît. Merci. Le pain sent bon.</t>
+          <t>narrateur|Aniss voit la boulangère, à la boulangerie.
+narrateur|De la farine blanche reste sur le tablier.
+narrateur|Le tablier sent le four, tout chaud.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu restes près de nous, Aniss.
+enfant-m|Oui, maman.
+papa|Tu veux que je tienne le filet ?
+enfant-m|S'il te plaît.
+narrateur|Le filet est rêche, un peu lourd déjà.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les mots gentils.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Aniss reste tout près de la jambe de maman.</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr"/>
@@ -2431,7 +2514,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2595,7 +2678,8 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr"/>
@@ -2623,7 +2707,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près de la boulangère. Le pain est chaud, dans le papier rêche. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2763,10 +2847,25 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à la boulangerie, près de la boulangère.
+narrateur|Le pain est chaud, dans le papier rêche.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2791,7 +2890,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué la boulangère. Il a le pain dans le filet. Le papier du pain reste tiède, dans le filet. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2931,7 +3030,18 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il a le pain dans le filet.
+narrateur|Le papier du pain reste tiède, dans le filet.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr"/>
@@ -2959,7 +3069,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près de la boulangère. Une pomme brille, près des croûtes dorées. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3099,7 +3209,18 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la boulangerie, près de la boulangère.
+narrateur|Une pomme brille, près des croûtes dorées.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr"/>
@@ -3127,7 +3248,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué la boulangère. Il a une pomme dans le filet. La pomme roule un peu, puis s'arrête. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3267,7 +3388,18 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il a une pomme dans le filet.
+narrateur|La pomme roule un peu, puis s'arrête.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr"/>
@@ -3295,7 +3427,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près de la boulangère. Le fromage sent le lait, à côté du four. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3435,7 +3567,18 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la boulangerie, près de la boulangère.
+narrateur|Le fromage sent le lait, à côté du four.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr"/>
@@ -3463,7 +3606,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué la boulangère. Il a un fromage dans le filet. Le fromage sent le lait, tout doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3603,7 +3746,18 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il a un fromage dans le filet.
+narrateur|Le fromage sent le lait, tout doux.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr"/>
@@ -3631,7 +3785,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Le voisin sourit. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit le voisin, à la boulangerie. Le voisin tient un sachet déjà tiède. Le sac du voisin est déjà un peu plein. Bonjour. Bonjour. Tu veux le filet un moment ? S'il te plaît. Papa tend le filet, tout doux. Merci, papa. Bravo. Bonjour. S'il te plaît. Merci. Le voisin hoche la tête, tout calme. Merci.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3771,7 +3925,19 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Le voisin sourit. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit le voisin, à la boulangerie.
+narrateur|Le voisin tient un sachet déjà tiède.
+narrateur|Le sac du voisin est déjà un peu plein.
+enfant-m|Bonjour.
+maman|Bonjour.
+papa|Tu veux le filet un moment ?
+enfant-m|S'il te plaît.
+narrateur|Papa tend le filet, tout doux.
+enfant-m|Merci, papa.
+maman|Bravo.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Le voisin hoche la tête, tout calme.
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr"/>
@@ -3799,7 +3965,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3963,7 +4129,8 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr"/>
@@ -3991,7 +4158,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près du voisin. Le voisin glisse le pain dans son filet. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4131,10 +4298,25 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à la boulangerie, près du voisin.
+narrateur|Le voisin glisse le pain dans son filet.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4159,7 +4341,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué le voisin. Il a le pain dans le filet. Le sachet du voisin fait un bruit de papier. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4299,7 +4481,18 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué le voisin.
+narrateur|Il a le pain dans le filet.
+narrateur|Le sachet du voisin fait un bruit de papier.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr"/>
@@ -4327,7 +4520,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près du voisin. Le voisin a une pomme, tout lisse. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4467,7 +4660,18 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la boulangerie, près du voisin.
+narrateur|Le voisin a une pomme, tout lisse.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr"/>
@@ -4495,7 +4699,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué le voisin. Il a une pomme dans le filet. Une croûte dore encore, derrière la vitre. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4635,7 +4839,18 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué le voisin.
+narrateur|Il a une pomme dans le filet.
+narrateur|Une croûte dore encore, derrière la vitre.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr"/>
@@ -4663,7 +4878,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près du voisin. Le voisin a un fromage, tout blanc. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4803,7 +5018,18 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la boulangerie, près du voisin.
+narrateur|Le voisin a un fromage, tout blanc.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr"/>
@@ -4831,7 +5057,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué le voisin. Il a un fromage dans le filet. La cloche de la porte fait ding, encore. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4971,7 +5197,18 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué le voisin.
+narrateur|Il a un fromage dans le filet.
+narrateur|La cloche de la porte fait ding, encore.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr"/>
@@ -4999,7 +5236,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>La maîtresse est là. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit la maîtresse, à la boulangerie. La maîtresse choisit un petit pain doré. Son panier a un linge à carreaux. Bonjour. Bonjour. Tu veux un fruit, Aniss ? S'il te plaît. Maman tend le filet, tout ouvert. Merci, maman. Bravo, Aniss. Bonjour. S'il te plaît. Merci. La maîtresse range un fruit, tout doux. On reste ensemble.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5139,7 +5376,19 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|La maîtresse est là. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit la maîtresse, à la boulangerie.
+narrateur|La maîtresse choisit un petit pain doré.
+narrateur|Son panier a un linge à carreaux.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu veux un fruit, Aniss ?
+enfant-m|S'il te plaît.
+narrateur|Maman tend le filet, tout ouvert.
+enfant-m|Merci, maman.
+papa|Bravo, Aniss.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|La maîtresse range un fruit, tout doux.
+papa|On reste ensemble.</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr"/>
@@ -5167,7 +5416,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5331,7 +5580,8 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr"/>
@@ -5359,7 +5609,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près de la maîtresse. La maîtresse a le pain contre le cartable. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5499,10 +5749,25 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à la boulangerie, près de la maîtresse.
+narrateur|La maîtresse a le pain contre le cartable.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5527,7 +5792,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué la maîtresse. Il a le pain dans le filet. Le cartable de la maîtresse est un peu lourd. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5667,7 +5932,18 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a le pain dans le filet.
+narrateur|Le cartable de la maîtresse est un peu lourd.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr"/>
@@ -5695,7 +5971,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près de la maîtresse. La maîtresse a une pomme dans la poche. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5835,7 +6111,18 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la boulangerie, près de la maîtresse.
+narrateur|La maîtresse a une pomme dans la poche.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr"/>
@@ -5863,7 +6150,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué la maîtresse. Il a une pomme dans le filet. La farine reste blanche, sur le bois. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6003,7 +6290,18 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a une pomme dans le filet.
+narrateur|La farine reste blanche, sur le bois.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr"/>
@@ -6031,7 +6329,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la boulangerie, près de la maîtresse. La maîtresse a un fromage, tout frais. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6171,7 +6469,18 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à la boulangerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la boulangerie, près de la maîtresse.
+narrateur|La maîtresse a un fromage, tout frais.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr"/>
@@ -6199,7 +6508,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la boulangerie. Il a salué la maîtresse. Il a un fromage dans le filet. L'air chaud de la boutique caresse les joues. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6339,7 +6648,18 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la boulangerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a un fromage dans le filet.
+narrateur|L'air chaud de la boutique caresse les joues.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr"/>
@@ -6367,7 +6687,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>À l'étal, Jules dit bonjour. Il dit s'il te plaît pour une pomme. Il dit merci.</t>
+          <t>Aniss s'arrête à l'étal des fruits. Les caisses sont rouges, un peu humides. Une balance de fer attend, tout calme. Bonjour. Bonjour. Tu veux une pomme, Aniss ? S'il te plaît. La pomme est lisse, encore un peu froide. Merci, papa. Bravo. Tu as demandé, puis remercié. On dit aussi bonjour. Bonjour. Une fraise brille, tout près du filet.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6507,7 +6827,20 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|À l'étal, Jules dit bonjour. Il dit s'il te plaît pour une pomme. Il dit merci.</t>
+          <t>narrateur|Aniss s'arrête à l'étal des fruits.
+narrateur|Les caisses sont rouges, un peu humides.
+narrateur|Une balance de fer attend, tout calme.
+enfant-m|Bonjour.
+maman|Bonjour.
+papa|Tu veux une pomme, Aniss ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, encore un peu froide.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as demandé, puis remercié.
+papa|On dit aussi bonjour.
+enfant-m|Bonjour.
+narrateur|Une fraise brille, tout près du filet.</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr"/>
@@ -6719,7 +7052,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Bonjour. S'il te plaît. Merci.</t>
+          <t>Oui. On dit bonjour. S'il te plaît. Merci. Aniss pose la pomme dans le filet. Bravo. Tu as demandé gentiment. S'il te plaît. C'est ça.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6863,7 +7196,14 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Oui.
+papa|On dit bonjour.
+maman|S'il te plaît. Merci.
+narrateur|Aniss pose la pomme dans le filet.
+papa|Bravo.
+papa|Tu as demandé gentiment.
+enfant-m|S'il te plaît.
+maman|C'est ça.</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr"/>
@@ -6891,7 +7231,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>Qui est là, près d'Aniss ? La boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7059,7 +7399,8 @@
       </c>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>narrateur|Qui est là, près d'Aniss ?
+papa|La boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr"/>
@@ -7087,7 +7428,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>À l'étal, la boulangère passe. Bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit la boulangère, à l'étal des fruits. La boulangère pèse une poire, tout doux. Le tablier sent le four, tout chaud. Bonjour. Bonjour. Tu restes près de nous, Aniss. Oui, maman. Tu veux que je tienne le filet ? S'il te plaît. Le filet est rêche, un peu lourd déjà. Merci, papa. Bravo. Tu as dit les mots gentils. Bonjour. S'il te plaît. Merci. Aniss reste tout près de la jambe de maman.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7227,7 +7568,21 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|À l'étal, la boulangère passe. Bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit la boulangère, à l'étal des fruits.
+narrateur|La boulangère pèse une poire, tout doux.
+narrateur|Le tablier sent le four, tout chaud.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu restes près de nous, Aniss.
+enfant-m|Oui, maman.
+papa|Tu veux que je tienne le filet ?
+enfant-m|S'il te plaît.
+narrateur|Le filet est rêche, un peu lourd déjà.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les mots gentils.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Aniss reste tout près de la jambe de maman.</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr"/>
@@ -7255,7 +7610,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7419,7 +7774,8 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr"/>
@@ -7447,7 +7803,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près de la boulangère. Le pain dore, près des caisses de fruits. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7587,10 +7943,25 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près de la boulangère.
+narrateur|Le pain dore, près des caisses de fruits.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7615,7 +7986,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué la boulangère. Il a le pain dans le filet. Une fraise brille encore, dans la caisse. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7755,7 +8126,18 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué la boulangère.
+narrateur|Il a le pain dans le filet.
+narrateur|Une fraise brille encore, dans la caisse.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr"/>
@@ -7783,7 +8165,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près de la boulangère. La pomme est rouge, encore un peu humide. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7923,7 +8305,18 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près de la boulangère.
+narrateur|La pomme est rouge, encore un peu humide.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr"/>
@@ -7951,7 +8344,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué la boulangère. Il a une pomme dans le filet. La balance fait un petit clic. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8091,7 +8484,18 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué la boulangère.
+narrateur|Il a une pomme dans le filet.
+narrateur|La balance fait un petit clic.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr"/>
@@ -8119,7 +8523,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près de la boulangère. Le fromage est posé loin des fraises. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8259,7 +8663,18 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près de la boulangère.
+narrateur|Le fromage est posé loin des fraises.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr"/>
@@ -8287,7 +8702,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué la boulangère. Il a un fromage dans le filet. Le filet de maman s'alourdit, tout doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8427,7 +8842,18 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué la boulangère.
+narrateur|Il a un fromage dans le filet.
+narrateur|Le filet de maman s'alourdit, tout doux.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr"/>
@@ -8455,7 +8881,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Le voisin prend une poire. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit le voisin, à l'étal des fruits. Le voisin prend une fraise, encore mouillée. Le sac du voisin est déjà un peu plein. Bonjour. Bonjour. Tu veux le filet un moment ? S'il te plaît. Papa tend le filet, tout doux. Merci, papa. Bravo. Bonjour. S'il te plaît. Merci. Le voisin hoche la tête, tout calme. Merci.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8595,7 +9021,19 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Le voisin prend une poire. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit le voisin, à l'étal des fruits.
+narrateur|Le voisin prend une fraise, encore mouillée.
+narrateur|Le sac du voisin est déjà un peu plein.
+enfant-m|Bonjour.
+maman|Bonjour.
+papa|Tu veux le filet un moment ?
+enfant-m|S'il te plaît.
+narrateur|Papa tend le filet, tout doux.
+enfant-m|Merci, papa.
+maman|Bravo.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Le voisin hoche la tête, tout calme.
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr"/>
@@ -8623,7 +9061,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8787,7 +9225,8 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr"/>
@@ -8815,7 +9254,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près du voisin. Le voisin a du pain, et une poire. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8955,10 +9394,25 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près du voisin.
+narrateur|Le voisin a du pain, et une poire.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8983,7 +9437,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué le voisin. Il a le pain dans le filet. Une poire reste verte, près de la pomme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9123,7 +9577,18 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué le voisin.
+narrateur|Il a le pain dans le filet.
+narrateur|Une poire reste verte, près de la pomme.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr"/>
@@ -9151,7 +9616,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près du voisin. Le voisin choisit une pomme, tout ronde. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9291,7 +9756,18 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près du voisin.
+narrateur|Le voisin choisit une pomme, tout ronde.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr"/>
@@ -9319,7 +9795,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué le voisin. Il a une pomme dans le filet. L'eau tremble encore dans l'ornière. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9459,7 +9935,18 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué le voisin.
+narrateur|Il a une pomme dans le filet.
+narrateur|L'eau tremble encore dans l'ornière.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr"/>
@@ -9487,7 +9974,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près du voisin. Le voisin a un fromage, près des cerises. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9627,7 +10114,18 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près du voisin.
+narrateur|Le voisin a un fromage, près des cerises.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr"/>
@@ -9655,7 +10153,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué le voisin. Il a un fromage dans le filet. La bâche claque, au-dessus des caisses. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9795,7 +10293,18 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué le voisin.
+narrateur|Il a un fromage dans le filet.
+narrateur|La bâche claque, au-dessus des caisses.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr"/>
@@ -9823,7 +10332,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>La maîtresse choisit des fraises. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit la maîtresse, à l'étal des fruits. La maîtresse choisit des fraises, tout rouge. Son panier a un linge à carreaux. Bonjour. Bonjour. Tu veux un fruit, Aniss ? S'il te plaît. Maman tend le filet, tout ouvert. Merci, maman. Bravo, Aniss. Bonjour. S'il te plaît. Merci. La maîtresse range un fruit, tout doux. On reste ensemble.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9963,7 +10472,19 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|La maîtresse choisit des fraises. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit la maîtresse, à l'étal des fruits.
+narrateur|La maîtresse choisit des fraises, tout rouge.
+narrateur|Son panier a un linge à carreaux.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu veux un fruit, Aniss ?
+enfant-m|S'il te plaît.
+narrateur|Maman tend le filet, tout ouvert.
+enfant-m|Merci, maman.
+papa|Bravo, Aniss.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|La maîtresse range un fruit, tout doux.
+papa|On reste ensemble.</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr"/>
@@ -9991,7 +10512,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10155,7 +10676,8 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr"/>
@@ -10183,7 +10705,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près de la maîtresse. La maîtresse a le pain, et des fraises. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10323,10 +10845,25 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près de la maîtresse.
+narrateur|La maîtresse a le pain, et des fraises.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10351,7 +10888,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué la maîtresse. Il a le pain dans le filet. Les fraises sentent le sucre, tout bas. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10491,7 +11028,18 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a le pain dans le filet.
+narrateur|Les fraises sentent le sucre, tout bas.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr"/>
@@ -10519,7 +11067,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près de la maîtresse. La maîtresse pèse une pomme, tout doux. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10659,7 +11207,18 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près de la maîtresse.
+narrateur|La maîtresse pèse une pomme, tout doux.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr"/>
@@ -10687,7 +11246,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué la maîtresse. Il a une pomme dans le filet. Un pigeon picore plus loin, tout calme. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10827,7 +11386,18 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a une pomme dans le filet.
+narrateur|Un pigeon picore plus loin, tout calme.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr"/>
@@ -10855,7 +11425,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à l'étal des fruits, près de la maîtresse. La maîtresse a un fromage, tout pâle. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -10995,7 +11565,18 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à l'étal des fruits. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à l'étal des fruits, près de la maîtresse.
+narrateur|La maîtresse a un fromage, tout pâle.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr"/>
@@ -11023,7 +11604,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu l'étal des fruits. Il a salué la maîtresse. Il a un fromage dans le filet. Le soleil revient sur les fruits rouges. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11163,7 +11744,18 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu l'étal des fruits.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a un fromage dans le filet.
+narrateur|Le soleil revient sur les fruits rouges.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr"/>
@@ -11191,7 +11783,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>À la fromagerie, Jules dit bonjour. S'il te plaît. Merci. Papa sourit.</t>
+          <t>Aniss entre à la fromagerie. L'air est frais, comme le marbre. Ça sent le lait, tout doux. Bonjour. Bonjour. Tu veux voir un fromage rond ? S'il te plaît. Le papier blanc fait un bruit doux. Merci, maman. Bravo, Aniss. Bonjour. S'il te plaît. Merci. Le filet reste ouvert, tout près de la jambe. On reste ensemble, ici.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11331,7 +11923,19 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|À la fromagerie, Jules dit bonjour. S'il te plaît. Merci. Papa sourit.</t>
+          <t>narrateur|Aniss entre à la fromagerie.
+narrateur|L'air est frais, comme le marbre.
+narrateur|Ça sent le lait, tout doux.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu veux voir un fromage rond ?
+enfant-m|S'il te plaît.
+narrateur|Le papier blanc fait un bruit doux.
+enfant-m|Merci, maman.
+papa|Bravo, Aniss.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet reste ouvert, tout près de la jambe.
+papa|On reste ensemble, ici.</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr"/>
@@ -11359,7 +11963,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>À la fromagerie, quels mots ?</t>
+          <t>À la fromagerie, Aniss salue. On dit bonjour, s'il te plaît, merci ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11515,7 +12119,8 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|À la fromagerie, quels mots ?</t>
+          <t>narrateur|À la fromagerie, Aniss salue.
+papa|On dit bonjour, s'il te plaît, merci ?</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr"/>
@@ -11543,7 +12148,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Jules a salué. Les trois mots sont là.</t>
+          <t>Oui. Les trois mots sont là. Bonjour. S'il te plaît. Merci. Aniss hoche la tête. Bravo, Aniss. Tu as fait du bon travail. Merci, maman.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11683,7 +12288,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Jules a salué. Les trois mots sont là.</t>
+          <t>narrateur|Oui.
+maman|Les trois mots sont là.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Aniss hoche la tête.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr"/>
@@ -11711,7 +12322,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>Qui est là, près d'Aniss ? La boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11879,7 +12490,8 @@
       </c>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la boulangère, le voisin, ou la maîtresse.</t>
+          <t>narrateur|Qui est là, près d'Aniss ?
+papa|La boulangère, le voisin, ou la maîtresse.</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr"/>
@@ -11907,7 +12519,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>À la fromagerie, la boulangère salue. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit la boulangère, à la fromagerie. La boulangère sent le lait, tout calme. Le tablier sent le four, tout chaud. Bonjour. Bonjour. Tu restes près de nous, Aniss. Oui, maman. Tu veux que je tienne le filet ? S'il te plaît. Le filet est rêche, un peu lourd déjà. Merci, papa. Bravo. Tu as dit les mots gentils. Bonjour. S'il te plaît. Merci. Aniss reste tout près de la jambe de maman.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12047,7 +12659,21 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|À la fromagerie, la boulangère salue. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit la boulangère, à la fromagerie.
+narrateur|La boulangère sent le lait, tout calme.
+narrateur|Le tablier sent le four, tout chaud.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu restes près de nous, Aniss.
+enfant-m|Oui, maman.
+papa|Tu veux que je tienne le filet ?
+enfant-m|S'il te plaît.
+narrateur|Le filet est rêche, un peu lourd déjà.
+enfant-m|Merci, papa.
+maman|Bravo.
+maman|Tu as dit les mots gentils.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Aniss reste tout près de la jambe de maman.</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr"/>
@@ -12075,7 +12701,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12239,7 +12865,8 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr"/>
@@ -12267,7 +12894,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près de la boulangère. Le pain reste au chaud, loin du lait. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12407,10 +13034,25 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à la fromagerie, près de la boulangère.
+narrateur|Le pain reste au chaud, loin du lait.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12435,7 +13077,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué la boulangère. Il a le pain dans le filet. Le marbre de la fromagerie reste froid. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12575,7 +13217,18 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il a le pain dans le filet.
+narrateur|Le marbre de la fromagerie reste froid.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr"/>
@@ -12603,7 +13256,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près de la boulangère. Une pomme attend sur le marbre froid. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12743,7 +13396,18 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la fromagerie, près de la boulangère.
+narrateur|Une pomme attend sur le marbre froid.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr"/>
@@ -12771,7 +13435,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué la boulangère. Il a une pomme dans le filet. Le papier blanc fait un bruit doux. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12911,7 +13575,18 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il a une pomme dans le filet.
+narrateur|Le papier blanc fait un bruit doux.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr"/>
@@ -12939,7 +13614,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la boulangère à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près de la boulangère. Le fromage est blanc, un peu tendre. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13079,7 +13754,18 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la boulangère à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la fromagerie, près de la boulangère.
+narrateur|Le fromage est blanc, un peu tendre.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr"/>
@@ -13107,7 +13793,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué la boulangère. Il a un fromage dans le filet. Ça sent le lait, tout près du filet. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13247,7 +13933,18 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué la boulangère.
+narrateur|Il a un fromage dans le filet.
+narrateur|Ça sent le lait, tout près du filet.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr"/>
@@ -13275,7 +13972,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Le voisin goûte. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit le voisin, à la fromagerie. Le voisin goûte un tout petit bout. Le sac du voisin est déjà un peu plein. Bonjour. Bonjour. Tu veux le filet un moment ? S'il te plaît. Papa tend le filet, tout doux. Merci, papa. Bravo. Bonjour. S'il te plaît. Merci. Le voisin hoche la tête, tout calme. Merci.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13415,7 +14112,19 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Le voisin goûte. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit le voisin, à la fromagerie.
+narrateur|Le voisin goûte un tout petit bout.
+narrateur|Le sac du voisin est déjà un peu plein.
+enfant-m|Bonjour.
+maman|Bonjour.
+papa|Tu veux le filet un moment ?
+enfant-m|S'il te plaît.
+narrateur|Papa tend le filet, tout doux.
+enfant-m|Merci, papa.
+maman|Bravo.
+papa|Bonjour. S'il te plaît. Merci.
+narrateur|Le voisin hoche la tête, tout calme.
+enfant-m|Merci.</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr"/>
@@ -13443,7 +14152,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13607,7 +14316,8 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr"/>
@@ -13635,7 +14345,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près du voisin. Le voisin a le pain, près du comptoir. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13775,10 +14485,25 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à la fromagerie, près du voisin.
+narrateur|Le voisin a le pain, près du comptoir.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13803,7 +14528,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué le voisin. Il a le pain dans le filet. Le voisin range son sachet, tout sage. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -13943,7 +14668,18 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué le voisin.
+narrateur|Il a le pain dans le filet.
+narrateur|Le voisin range son sachet, tout sage.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr"/>
@@ -13971,7 +14707,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près du voisin. Le voisin pose une pomme, tout loin. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14111,7 +14847,18 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la fromagerie, près du voisin.
+narrateur|Le voisin pose une pomme, tout loin.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr"/>
@@ -14139,7 +14886,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué le voisin. Il a une pomme dans le filet. Une pièce tinte, dans le porte-monnaie. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14279,7 +15026,18 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué le voisin.
+narrateur|Il a une pomme dans le filet.
+narrateur|Une pièce tinte, dans le porte-monnaie.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr"/>
@@ -14307,7 +15065,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint le voisin à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près du voisin. Le voisin a un fromage, tout rond. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14447,7 +15205,18 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint le voisin à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la fromagerie, près du voisin.
+narrateur|Le voisin a un fromage, tout rond.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr"/>
@@ -14475,7 +15244,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué le voisin. Il a un fromage dans le filet. Le thym sent encore, sur le pavé. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14615,7 +15384,18 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué le voisin.
+narrateur|Il a un fromage dans le filet.
+narrateur|Le thym sent encore, sur le pavé.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr"/>
@@ -14643,7 +15423,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>La maîtresse attend. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>Aniss voit la maîtresse, à la fromagerie. La maîtresse attend près du comptoir frais. Son panier a un linge à carreaux. Bonjour. Bonjour. Tu veux un fruit, Aniss ? S'il te plaît. Maman tend le filet, tout ouvert. Merci, maman. Bravo, Aniss. Bonjour. S'il te plaît. Merci. La maîtresse range un fruit, tout doux. On reste ensemble.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14783,7 +15563,19 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|La maîtresse attend. Jules dit bonjour. S'il te plaît. Merci.</t>
+          <t>narrateur|Aniss voit la maîtresse, à la fromagerie.
+narrateur|La maîtresse attend près du comptoir frais.
+narrateur|Son panier a un linge à carreaux.
+enfant-m|Bonjour.
+papa|Bonjour.
+maman|Tu veux un fruit, Aniss ?
+enfant-m|S'il te plaît.
+narrateur|Maman tend le filet, tout ouvert.
+enfant-m|Merci, maman.
+papa|Bravo, Aniss.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|La maîtresse range un fruit, tout doux.
+papa|On reste ensemble.</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr"/>
@@ -14811,7 +15603,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>Qu'est-ce qui va dans le filet ? Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -14975,7 +15767,8 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le pain, une pomme, ou un fromage.</t>
+          <t>narrateur|Qu'est-ce qui va dans le filet ?
+maman|Le pain, une pomme, ou un fromage.</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr"/>
@@ -15003,7 +15796,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près de la maîtresse. La maîtresse a le pain, tout contre elle. Bonjour. Tu veux le pain ? S'il te plaît. Le pain est tiède, contre les doigts. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15143,10 +15936,25 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a le pain. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|Aniss est encore à la fromagerie, près de la maîtresse.
+narrateur|La maîtresse a le pain, tout contre elle.
+enfant-m|Bonjour.
+maman|Tu veux le pain ?
+enfant-m|S'il te plaît.
+narrateur|Le pain est tiède, contre les doigts.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>papier</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15171,7 +15979,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué la maîtresse. Il a le pain dans le filet. La maîtresse dit au revoir, tout bas. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15311,7 +16119,18 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a le pain dans le filet.
+narrateur|La maîtresse dit au revoir, tout bas.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr"/>
@@ -15339,7 +16158,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près de la maîtresse. La maîtresse a une pomme, tout brillante. Bonjour. Tu veux une pomme ? S'il te plaît. La pomme est lisse, un peu froide. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15479,7 +16298,18 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a une pomme. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la fromagerie, près de la maîtresse.
+narrateur|La maîtresse a une pomme, tout brillante.
+enfant-m|Bonjour.
+maman|Tu veux une pomme ?
+enfant-m|S'il te plaît.
+narrateur|La pomme est lisse, un peu froide.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr"/>
@@ -15507,7 +16337,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué la maîtresse. Il a une pomme dans le filet. Le filet frotte la jambe, un peu rêche. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15647,7 +16477,18 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a une pomme dans le filet.
+narrateur|Le filet frotte la jambe, un peu rêche.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr"/>
@@ -15675,7 +16516,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Jules rejoint la maîtresse à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>Aniss est encore à la fromagerie, près de la maîtresse. La maîtresse a un fromage, tout frais. Bonjour. Tu veux un fromage ? S'il te plaît. Le fromage est frais, tout enveloppé. Merci. Bravo, Aniss. Tu as dit les trois mots. Bonjour. S'il te plaît. Merci. Le filet s'arrondit, tout doux. On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15815,7 +16656,18 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Jules rejoint la maîtresse à la fromagerie. Il a un fromage. Il a dit bonjour, s'il te plaît, merci. Papa dit bravo.</t>
+          <t>narrateur|Aniss est encore à la fromagerie, près de la maîtresse.
+narrateur|La maîtresse a un fromage, tout frais.
+enfant-m|Bonjour.
+maman|Tu veux un fromage ?
+enfant-m|S'il te plaît.
+narrateur|Le fromage est frais, tout enveloppé.
+enfant-m|Merci.
+papa|Bravo, Aniss.
+papa|Tu as dit les trois mots.
+maman|Bonjour. S'il te plaît. Merci.
+narrateur|Le filet s'arrondit, tout doux.
+papa|On a ce qu'il faut, maintenant.</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr"/>
@@ -15843,7 +16695,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Aniss a vu la fromagerie. Il a salué la maîtresse. Il a un fromage dans le filet. La maison n'est plus très loin, maintenant. Tu as dit bonjour. Tu as dit s'il te plaît. Et merci. Bravo, Aniss. Tu as fait du bon travail. Merci, maman. On rentre, le filet est plein. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -15983,7 +16835,18 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
+          <t>narrateur|Aniss a vu la fromagerie.
+narrateur|Il a salué la maîtresse.
+narrateur|Il a un fromage dans le filet.
+narrateur|La maison n'est plus très loin, maintenant.
+papa|Tu as dit bonjour.
+maman|Tu as dit s'il te plaît.
+papa|Et merci.
+maman|Bravo, Aniss.
+maman|Tu as fait du bon travail.
+enfant-m|Merci, maman.
+papa|On rentre, le filet est plein.
+narrateur|L'histoire est finie.</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr"/>
@@ -16005,7 +16868,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16050,6 +16913,13 @@
       <c r="A6" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>
